--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96196998</v>
+        <v>96196931</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>1958</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508085.4426311367</v>
+        <v>508008</v>
       </c>
       <c r="R2" t="n">
-        <v>6783135.771240801</v>
+        <v>6783134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96197023</v>
+        <v>96197008</v>
       </c>
       <c r="B3" t="n">
-        <v>88901</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2051</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508107.7456103972</v>
+        <v>508034</v>
       </c>
       <c r="R3" t="n">
-        <v>6782890.79743661</v>
+        <v>6782939</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96196990</v>
+        <v>96197023</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>2051</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508122.0611795587</v>
+        <v>508108</v>
       </c>
       <c r="R4" t="n">
-        <v>6783176.852268407</v>
+        <v>6782891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +957,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96197009</v>
+        <v>96197026</v>
       </c>
       <c r="B5" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256703</v>
+        <v>2051</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508029.3860823445</v>
+        <v>508055</v>
       </c>
       <c r="R5" t="n">
-        <v>6782933.064179665</v>
+        <v>6782859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1064,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1163,53 +1103,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96197007</v>
+        <v>96221111</v>
       </c>
       <c r="B6" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>256703</v>
+        <v>2051</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Furudal, V Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508007.5698497538</v>
+        <v>507996</v>
       </c>
       <c r="R6" t="n">
-        <v>6782966.778348611</v>
+        <v>6782986</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,27 +1179,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>avverkningsanmäld</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,76 +1193,98 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96197006</v>
+        <v>112390775</v>
       </c>
       <c r="B7" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>256703</v>
+        <v>2051</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507997.3843310855</v>
+        <v>507998</v>
       </c>
       <c r="R7" t="n">
-        <v>6782984.601679145</v>
+        <v>6782992</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,27 +1308,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>avverkningsanmäld</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1322,11 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
         </is>
@@ -1395,62 +1334,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96197005</v>
+        <v>130683161</v>
       </c>
       <c r="B8" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507985.2413769105</v>
+        <v>507996</v>
       </c>
       <c r="R8" t="n">
-        <v>6783013.51417678</v>
+        <v>6782913</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,27 +1411,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,71 +1432,61 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96196984</v>
+        <v>130683162</v>
       </c>
       <c r="B9" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>2051</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508236.9873059026</v>
+        <v>508114</v>
       </c>
       <c r="R9" t="n">
-        <v>6783195.44734856</v>
+        <v>6782892</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,27 +1513,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,71 +1534,61 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96196999</v>
+        <v>130683163</v>
       </c>
       <c r="B10" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508085.4426311367</v>
+        <v>508059</v>
       </c>
       <c r="R10" t="n">
-        <v>6783135.771240801</v>
+        <v>6782856</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,27 +1615,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,36 +1636,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96197026</v>
+        <v>96196928</v>
       </c>
       <c r="B11" t="n">
-        <v>88901</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2051</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1813,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508055.1592398504</v>
+        <v>507971</v>
       </c>
       <c r="R11" t="n">
-        <v>6782859.323727878</v>
+        <v>6783024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,19 +1720,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1895,37 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96197024</v>
+        <v>96196932</v>
       </c>
       <c r="B12" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1935,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508108.7162640356</v>
+        <v>508008</v>
       </c>
       <c r="R12" t="n">
-        <v>6782888.870275008</v>
+        <v>6783134</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1968,19 +1827,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2017,37 +1866,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96196933</v>
+        <v>96196935</v>
       </c>
       <c r="B13" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2057,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508007.6729273635</v>
+        <v>508014</v>
       </c>
       <c r="R13" t="n">
-        <v>6783133.664023995</v>
+        <v>6783175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2090,19 +1934,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2139,37 +1973,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96196996</v>
+        <v>96196992</v>
       </c>
       <c r="B14" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2179,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508069.4194561404</v>
+        <v>508080</v>
       </c>
       <c r="R14" t="n">
-        <v>6783171.425655571</v>
+        <v>6783169</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2212,19 +2041,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2261,37 +2080,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96197002</v>
+        <v>96196994</v>
       </c>
       <c r="B15" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2301,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508068.3276895816</v>
+        <v>508073</v>
       </c>
       <c r="R15" t="n">
-        <v>6783015.633148991</v>
+        <v>6783174</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2334,19 +2148,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2383,15 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96197008</v>
+        <v>130225633</v>
       </c>
       <c r="B16" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,34 +2198,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1958</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508034.2038269797</v>
+        <v>508091</v>
       </c>
       <c r="R16" t="n">
-        <v>6782938.863304546</v>
+        <v>6782799</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2453,27 +2252,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2484,71 +2273,61 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96196983</v>
+        <v>130225634</v>
       </c>
       <c r="B17" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508236.4782625315</v>
+        <v>508082</v>
       </c>
       <c r="R17" t="n">
-        <v>6783206.539226788</v>
+        <v>6783208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2575,27 +2354,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,71 +2375,61 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96196985</v>
+        <v>130225636</v>
       </c>
       <c r="B18" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>508207.06342996</v>
+        <v>507960</v>
       </c>
       <c r="R18" t="n">
-        <v>6783184.284277339</v>
+        <v>6782965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2697,27 +2456,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2728,71 +2477,61 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96196934</v>
+        <v>130683147</v>
       </c>
       <c r="B19" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508007.6136198686</v>
+        <v>508082</v>
       </c>
       <c r="R19" t="n">
-        <v>6783159.708881355</v>
+        <v>6783169</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2819,27 +2558,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2850,71 +2579,61 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96196987</v>
+        <v>130683148</v>
       </c>
       <c r="B20" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>508199.3602991366</v>
+        <v>508007</v>
       </c>
       <c r="R20" t="n">
-        <v>6783173.173167687</v>
+        <v>6783132</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2941,27 +2660,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,71 +2681,61 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96196995</v>
+        <v>130209297</v>
       </c>
       <c r="B21" t="n">
-        <v>88938</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6039941</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508059.3049568093</v>
+        <v>508080</v>
       </c>
       <c r="R21" t="n">
-        <v>6783158.380030197</v>
+        <v>6782860</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3063,67 +2762,47 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96196932</v>
+        <v>96197024</v>
       </c>
       <c r="B22" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3131,21 +2810,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3155,10 +2834,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508007.6729273635</v>
+        <v>508109</v>
       </c>
       <c r="R22" t="n">
-        <v>6783133.664023995</v>
+        <v>6782889</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3188,19 +2867,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3237,37 +2906,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96197025</v>
+        <v>96196934</v>
       </c>
       <c r="B23" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3277,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>508096.638693126</v>
+        <v>508008</v>
       </c>
       <c r="R23" t="n">
-        <v>6782888.842449088</v>
+        <v>6783160</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3310,19 +2974,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3359,37 +3013,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96196930</v>
+        <v>96197028</v>
       </c>
       <c r="B24" t="n">
-        <v>88938</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6039941</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3399,10 +3048,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507998.1344040674</v>
+        <v>508033</v>
       </c>
       <c r="R24" t="n">
-        <v>6783079.622460406</v>
+        <v>6782846</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3432,21 +3081,11 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-09-19</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
           <t>avverkningsanmäld</t>
@@ -3456,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3481,50 +3120,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96197003</v>
+        <v>130209299</v>
       </c>
       <c r="B25" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>508060.1450852167</v>
+        <v>508139</v>
       </c>
       <c r="R25" t="n">
-        <v>6783002.591380254</v>
+        <v>6782801</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3551,27 +3185,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3582,36 +3206,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96196997</v>
+        <v>130225652</v>
       </c>
       <c r="B26" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3619,34 +3233,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>508069.4194561404</v>
+        <v>507960</v>
       </c>
       <c r="R26" t="n">
-        <v>6783171.425655571</v>
+        <v>6782958</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3673,27 +3290,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Sveaskogs naturvärdesinvenntering.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3702,38 +3309,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96196992</v>
+        <v>96196984</v>
       </c>
       <c r="B27" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>508080.0535138128</v>
+        <v>508237</v>
       </c>
       <c r="R27" t="n">
-        <v>6783168.556204576</v>
+        <v>6783195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3798,19 +3396,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3847,15 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96197000</v>
+        <v>96196987</v>
       </c>
       <c r="B28" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3863,21 +3446,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3887,10 +3470,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>508096.5876411292</v>
+        <v>508199</v>
       </c>
       <c r="R28" t="n">
-        <v>6783120.845048815</v>
+        <v>6783173</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3920,19 +3503,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3969,19 +3542,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96196991</v>
+        <v>96196988</v>
       </c>
       <c r="B29" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4009,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508100.7808407518</v>
+        <v>508182</v>
       </c>
       <c r="R29" t="n">
-        <v>6783187.896308683</v>
+        <v>6783169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4042,19 +3610,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4091,37 +3649,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96196931</v>
+        <v>96196989</v>
       </c>
       <c r="B30" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1958</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4131,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508007.6729273635</v>
+        <v>508166</v>
       </c>
       <c r="R30" t="n">
-        <v>6783133.664023995</v>
+        <v>6783173</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4164,19 +3717,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4213,19 +3756,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96196988</v>
+        <v>96196990</v>
       </c>
       <c r="B31" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4253,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>508181.9801024392</v>
+        <v>508122</v>
       </c>
       <c r="R31" t="n">
-        <v>6783168.791882421</v>
+        <v>6783177</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4286,19 +3824,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4335,15 +3863,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96197004</v>
+        <v>96196991</v>
       </c>
       <c r="B32" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4351,21 +3874,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4375,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508025.3595037961</v>
+        <v>508101</v>
       </c>
       <c r="R32" t="n">
-        <v>6783003.958828855</v>
+        <v>6783188</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4408,19 +3931,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4457,19 +3970,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96196989</v>
+        <v>96196996</v>
       </c>
       <c r="B33" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4497,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>508166.030017411</v>
+        <v>508069</v>
       </c>
       <c r="R33" t="n">
-        <v>6783172.613299213</v>
+        <v>6783171</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,19 +4038,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4579,37 +4077,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96196929</v>
+        <v>96196998</v>
       </c>
       <c r="B34" t="n">
-        <v>88938</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6039941</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4619,10 +4112,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507987.5319153311</v>
+        <v>508085</v>
       </c>
       <c r="R34" t="n">
-        <v>6783068.50489684</v>
+        <v>6783136</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4652,21 +4145,11 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-09-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
           <t>avverkningsanmäld</t>
@@ -4676,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4701,15 +4184,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96196994</v>
+        <v>96197001</v>
       </c>
       <c r="B35" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4717,21 +4195,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4741,10 +4219,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>508073.2773245224</v>
+        <v>508087</v>
       </c>
       <c r="R35" t="n">
-        <v>6783174.328377247</v>
+        <v>6783110</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4774,19 +4252,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4823,15 +4291,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96196936</v>
+        <v>96197002</v>
       </c>
       <c r="B36" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4839,21 +4302,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4863,10 +4326,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>508038.9114470968</v>
+        <v>508068</v>
       </c>
       <c r="R36" t="n">
-        <v>6783204.152798223</v>
+        <v>6783016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4896,19 +4359,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4945,15 +4398,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96196939</v>
+        <v>96197003</v>
       </c>
       <c r="B37" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4961,21 +4409,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4985,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>508134.8651152735</v>
+        <v>508060</v>
       </c>
       <c r="R37" t="n">
-        <v>6783280.094831403</v>
+        <v>6783003</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5018,19 +4466,9 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5067,15 +4505,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96196935</v>
+        <v>112390723</v>
       </c>
       <c r="B38" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5083,37 +4516,48 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>508014.3424630371</v>
+        <v>507956</v>
       </c>
       <c r="R38" t="n">
-        <v>6783174.67587836</v>
+        <v>6783078</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5137,27 +4581,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>avverkningsanmäld</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5166,10 +4595,11 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AI38" t="inlineStr">
+      <c r="AH38" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
         </is>
@@ -5177,31 +4607,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96197001</v>
+        <v>130209280</v>
       </c>
       <c r="B39" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5225,14 +4650,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>508086.9517324214</v>
+        <v>508292</v>
       </c>
       <c r="R39" t="n">
-        <v>6783109.729538705</v>
+        <v>6783201</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5259,27 +4684,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>avverkningsanmäld</t>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5290,36 +4705,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96196928</v>
+        <v>130225549</v>
       </c>
       <c r="B40" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5327,34 +4732,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507971.2078393883</v>
+        <v>507999</v>
       </c>
       <c r="R40" t="n">
-        <v>6783024.093646547</v>
+        <v>6783016</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5381,27 +4786,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>avverkningsanmäld</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5412,85 +4802,64 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96221143</v>
+        <v>96197034</v>
       </c>
       <c r="B41" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>256703</v>
+        <v>4745</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Furudal, V Tillhedstjärnen, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507965.079591089</v>
+        <v>508094</v>
       </c>
       <c r="R41" t="n">
-        <v>6782957.035058565</v>
+        <v>6782770</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5514,22 +4883,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5538,103 +4902,71 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AH41" t="inlineStr">
+      <c r="AI41" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96221111</v>
+        <v>130225548</v>
       </c>
       <c r="B42" t="n">
-        <v>89829</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2051</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Furudal, V Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507996</v>
+        <v>507978</v>
       </c>
       <c r="R42" t="n">
-        <v>6782986</v>
+        <v>6783003</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5658,12 +4990,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5672,103 +5004,66 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96221099</v>
+        <v>130225628</v>
       </c>
       <c r="B43" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>256703</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Furudal, V Tillhedstjärnen, Dlr</t>
+          <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>508004.448433154</v>
+        <v>508114</v>
       </c>
       <c r="R43" t="n">
-        <v>6783064.684755801</v>
+        <v>6783216</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5792,110 +5087,74 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>kan vara R primulina</t>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>96221109</v>
+        <v>96221156</v>
       </c>
       <c r="B44" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91424</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>256703</v>
+        <v>5733</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5911,10 +5170,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507995.4497791897</v>
+        <v>507957</v>
       </c>
       <c r="R44" t="n">
-        <v>6782985.561953882</v>
+        <v>6782932</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5944,19 +5203,14 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>obeskriven "heath/kangas" (aff. flavigelatinosa)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6004,64 +5258,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112390775</v>
+        <v>96196933</v>
       </c>
       <c r="B45" t="n">
-        <v>89162</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507997</v>
+        <v>508008</v>
       </c>
       <c r="R45" t="n">
-        <v>6782992</v>
+        <v>6783134</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6085,12 +5323,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6099,11 +5342,10 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AH45" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
         </is>
@@ -6111,76 +5353,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112390723</v>
+        <v>96196936</v>
       </c>
       <c r="B46" t="n">
-        <v>90926</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507957</v>
+        <v>508039</v>
       </c>
       <c r="R46" t="n">
-        <v>6783078</v>
+        <v>6783204</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6204,12 +5430,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6218,11 +5449,10 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AH46" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
         </is>
@@ -6230,68 +5460,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112390786</v>
+        <v>96196938</v>
       </c>
       <c r="B47" t="n">
-        <v>89172</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507999</v>
+        <v>508105</v>
       </c>
       <c r="R47" t="n">
-        <v>6783054</v>
+        <v>6783225</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6315,12 +5537,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6329,11 +5556,10 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AH47" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
         </is>
@@ -6341,68 +5567,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112390818</v>
+        <v>96196939</v>
       </c>
       <c r="B48" t="n">
-        <v>89199</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6039941</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507999</v>
+        <v>508135</v>
       </c>
       <c r="R48" t="n">
-        <v>6783054</v>
+        <v>6783280</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6426,82 +5644,87 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128340151</v>
+        <v>96196982</v>
       </c>
       <c r="B49" t="n">
-        <v>91002</v>
+        <v>93235</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Furudal, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>508002</v>
+        <v>508260</v>
       </c>
       <c r="R49" t="n">
-        <v>6783134</v>
+        <v>6783214</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6528,17 +5751,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6547,68 +5770,68 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128340152</v>
+        <v>96196983</v>
       </c>
       <c r="B50" t="n">
-        <v>91039</v>
+        <v>93235</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6039941</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Furudal, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>508033</v>
+        <v>508236</v>
       </c>
       <c r="R50" t="n">
-        <v>6783194</v>
+        <v>6783207</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6635,17 +5858,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6656,65 +5879,66 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128340150</v>
+        <v>96196985</v>
       </c>
       <c r="B51" t="n">
-        <v>91010</v>
+        <v>93235</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Furudal, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507991</v>
+        <v>508207</v>
       </c>
       <c r="R51" t="n">
-        <v>6782991</v>
+        <v>6783184</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6741,17 +5965,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6762,65 +5986,66 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128340148</v>
+        <v>96196997</v>
       </c>
       <c r="B52" t="n">
-        <v>91039</v>
+        <v>93235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6039941</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Furudal, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>508080</v>
+        <v>508069</v>
       </c>
       <c r="R52" t="n">
-        <v>6783012</v>
+        <v>6783171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6847,17 +6072,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6868,26 +6093,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128533297</v>
+        <v>96196999</v>
       </c>
       <c r="B53" t="n">
-        <v>92844</v>
+        <v>93235</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6895,38 +6125,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3100</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Furudal, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>508080</v>
+        <v>508085</v>
       </c>
       <c r="R53" t="n">
-        <v>6782860</v>
+        <v>6783136</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6953,17 +6179,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6974,65 +6200,66 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128533295</v>
+        <v>96197000</v>
       </c>
       <c r="B54" t="n">
-        <v>92819</v>
+        <v>93235</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Furudal, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508139</v>
+        <v>508097</v>
       </c>
       <c r="R54" t="n">
-        <v>6782801</v>
+        <v>6783121</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7059,17 +6286,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7080,61 +6307,66 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130225626</v>
+        <v>96197004</v>
       </c>
       <c r="B55" t="n">
-        <v>90571</v>
+        <v>93235</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6286</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>508123</v>
+        <v>508025</v>
       </c>
       <c r="R55" t="n">
-        <v>6783277</v>
+        <v>6783004</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7161,17 +6393,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Sveaskogs naturvärdesinventering.</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7182,26 +6414,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130225628</v>
+        <v>96197005</v>
       </c>
       <c r="B56" t="n">
-        <v>92692</v>
+        <v>93235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7209,34 +6446,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508114</v>
+        <v>507985</v>
       </c>
       <c r="R56" t="n">
-        <v>6783216</v>
+        <v>6783014</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7263,17 +6500,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Sveaskogs naturvärdesinventering.</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7284,16 +6521,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7303,7 +6545,7 @@
         <v>130225558</v>
       </c>
       <c r="B57" t="n">
-        <v>93085</v>
+        <v>93235</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7397,48 +6639,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130225650</v>
+        <v>130225559</v>
       </c>
       <c r="B58" t="n">
-        <v>91292</v>
+        <v>93235</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6039941</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>508027</v>
+        <v>508174</v>
       </c>
       <c r="R58" t="n">
-        <v>6783219</v>
+        <v>6783134</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7465,17 +6704,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Sveaskogs naturvärdesinvenntering.</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7484,7 +6718,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7506,7 +6739,7 @@
         <v>130225560</v>
       </c>
       <c r="B59" t="n">
-        <v>93085</v>
+        <v>93235</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7600,10 +6833,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130225548</v>
+        <v>130225561</v>
       </c>
       <c r="B60" t="n">
-        <v>92692</v>
+        <v>93235</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7611,21 +6844,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7635,10 +6868,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507978</v>
+        <v>508124</v>
       </c>
       <c r="R60" t="n">
-        <v>6783003</v>
+        <v>6783113</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7697,32 +6930,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130225610</v>
+        <v>130225562</v>
       </c>
       <c r="B61" t="n">
-        <v>97834</v>
+        <v>93235</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7732,10 +6965,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>508173</v>
+        <v>508080</v>
       </c>
       <c r="R61" t="n">
-        <v>6783278</v>
+        <v>6783068</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7762,17 +6995,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Sveaskogs naturvärdesinventering.</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7799,32 +7027,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130225549</v>
+        <v>130683146</v>
       </c>
       <c r="B62" t="n">
-        <v>93059</v>
+        <v>93235</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7834,10 +7062,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507999</v>
+        <v>508070</v>
       </c>
       <c r="R62" t="n">
-        <v>6783016</v>
+        <v>6783171</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7870,6 +7098,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7896,32 +7129,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130225552</v>
+        <v>130683155</v>
       </c>
       <c r="B63" t="n">
-        <v>97834</v>
+        <v>93235</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7931,10 +7164,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507997</v>
+        <v>508126</v>
       </c>
       <c r="R63" t="n">
-        <v>6783014</v>
+        <v>6783279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7961,12 +7194,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7993,10 +7231,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130225634</v>
+        <v>130683157</v>
       </c>
       <c r="B64" t="n">
-        <v>93063</v>
+        <v>93235</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8004,21 +7242,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8028,10 +7266,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508082</v>
+        <v>508259</v>
       </c>
       <c r="R64" t="n">
-        <v>6783208</v>
+        <v>6783203</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8068,7 +7306,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Sveaskogs naturvärdesinventering.</t>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8095,10 +7333,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130225562</v>
+        <v>130683160</v>
       </c>
       <c r="B65" t="n">
-        <v>93085</v>
+        <v>93235</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8130,10 +7368,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>508080</v>
+        <v>508206</v>
       </c>
       <c r="R65" t="n">
-        <v>6783068</v>
+        <v>6783188</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8160,12 +7398,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8195,7 +7438,7 @@
         <v>130225546</v>
       </c>
       <c r="B66" t="n">
-        <v>90571</v>
+        <v>90710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8289,32 +7532,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130225559</v>
+        <v>130225626</v>
       </c>
       <c r="B67" t="n">
-        <v>93085</v>
+        <v>90710</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>6286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8324,10 +7567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>508174</v>
+        <v>508123</v>
       </c>
       <c r="R67" t="n">
-        <v>6783134</v>
+        <v>6783277</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8354,12 +7597,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8386,32 +7634,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130225636</v>
+        <v>130209276</v>
       </c>
       <c r="B68" t="n">
-        <v>93063</v>
+        <v>97989</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8421,10 +7669,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507960</v>
+        <v>507981</v>
       </c>
       <c r="R68" t="n">
-        <v>6782965</v>
+        <v>6783241</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8451,12 +7699,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8488,32 +7736,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130225561</v>
+        <v>130209277</v>
       </c>
       <c r="B69" t="n">
-        <v>93085</v>
+        <v>97989</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8523,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>508124</v>
+        <v>508030</v>
       </c>
       <c r="R69" t="n">
-        <v>6783113</v>
+        <v>6783236</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8553,12 +7801,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8585,10 +7838,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130225652</v>
+        <v>130225552</v>
       </c>
       <c r="B70" t="n">
-        <v>93047</v>
+        <v>97989</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8596,37 +7849,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507960</v>
+        <v>507997</v>
       </c>
       <c r="R70" t="n">
-        <v>6782958</v>
+        <v>6783014</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8653,17 +7903,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Sveaskogs naturvärdesinvenntering.</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8672,7 +7917,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8691,32 +7935,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130225624</v>
+        <v>130225610</v>
       </c>
       <c r="B71" t="n">
-        <v>91292</v>
+        <v>97989</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6039941</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8726,10 +7970,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>508161</v>
+        <v>508173</v>
       </c>
       <c r="R71" t="n">
-        <v>6783144</v>
+        <v>6783278</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8793,45 +8037,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130225630</v>
+        <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91263</v>
+        <v>91441</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>256703</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tallfingersvamp</t>
-        </is>
+        <v>233197</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramaria subtilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Coker) Schild, 1982</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>508149</v>
+        <v>507996</v>
       </c>
       <c r="R72" t="n">
-        <v>6783300</v>
+        <v>6783143</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8858,17 +8100,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Sveaskogs naturvärdesinventering.</t>
+          <t>Konsulterat och skickat kollekt till JO Hermansson. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8877,6 +8119,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8895,45 +8138,43 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130683162</v>
+        <v>130209286</v>
       </c>
       <c r="B73" t="n">
-        <v>91293</v>
+        <v>91441</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2051</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Rotfingersvamp</t>
-        </is>
+        <v>233197</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Ramaria subtilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Coker) Schild, 1982</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>508114</v>
+        <v>508002</v>
       </c>
       <c r="R73" t="n">
-        <v>6782892</v>
+        <v>6783134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8970,7 +8211,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
+          <t>Konsulterat och skickat kollekt till JO Hermansson. Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8979,6 +8220,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8997,10 +8239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130683157</v>
+        <v>96196937</v>
       </c>
       <c r="B74" t="n">
-        <v>93133</v>
+        <v>91402</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9008,34 +8250,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>508259</v>
+        <v>508087</v>
       </c>
       <c r="R74" t="n">
-        <v>6783203</v>
+        <v>6783225</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9062,17 +8304,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9083,26 +8325,31 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130683160</v>
+        <v>96196940</v>
       </c>
       <c r="B75" t="n">
-        <v>93133</v>
+        <v>91402</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9110,34 +8357,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>508206</v>
+        <v>508162</v>
       </c>
       <c r="R75" t="n">
-        <v>6783188</v>
+        <v>6783309</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9164,17 +8411,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9185,26 +8432,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130683147</v>
+        <v>96197006</v>
       </c>
       <c r="B76" t="n">
-        <v>93111</v>
+        <v>91402</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9212,34 +8464,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>508082</v>
+        <v>507997</v>
       </c>
       <c r="R76" t="n">
-        <v>6783169</v>
+        <v>6782985</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9266,17 +8518,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9287,26 +8539,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130683148</v>
+        <v>96197007</v>
       </c>
       <c r="B77" t="n">
-        <v>93111</v>
+        <v>91402</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9314,34 +8571,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>508007</v>
+        <v>508008</v>
       </c>
       <c r="R77" t="n">
-        <v>6783132</v>
+        <v>6782967</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9368,17 +8625,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9389,61 +8646,66 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130683163</v>
+        <v>96197009</v>
       </c>
       <c r="B78" t="n">
-        <v>91293</v>
+        <v>91402</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2051</v>
+        <v>256703</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>508059</v>
+        <v>508029</v>
       </c>
       <c r="R78" t="n">
-        <v>6782856</v>
+        <v>6782933</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9470,17 +8732,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9491,26 +8753,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130683155</v>
+        <v>96197010</v>
       </c>
       <c r="B79" t="n">
-        <v>93133</v>
+        <v>91402</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9518,34 +8785,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tillhedstjärn, Dlr</t>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>508126</v>
+        <v>508000</v>
       </c>
       <c r="R79" t="n">
-        <v>6783279</v>
+        <v>6782924</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9572,17 +8839,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Återfynd av tidigare registrerat fynd från 2021. Sveaskogs naturvärdesinventering.</t>
+          <t>avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9593,19 +8860,2208 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>96197025</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>508097</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6782889</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>96220942</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Furudal, V Tillhedstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>507918</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6783056</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>96221099</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Furudal, V Tillhedstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>508004</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6783065</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>kan vara R primulina</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>96221109</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Furudal, V Tillhedstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>507996</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6782986</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>96221143</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Furudal, V Tillhedstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>507965</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6782957</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>112390786</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>507998</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6783054</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>130209278</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>508044</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6783224</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
           <t>Maria Hindemo</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
+      <c r="AX86" t="inlineStr">
         <is>
           <t>Maria Hindemo</t>
         </is>
       </c>
-      <c r="AY79" t="inlineStr"/>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>130209293</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>507991</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6782991</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>130209295</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>508016</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6782919</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>130209301</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>508086</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6782779</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>130225630</v>
+      </c>
+      <c r="B90" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>508149</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6783300</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>96196929</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>507988</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6783069</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>96196930</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>507998</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6783080</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>96196995</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>sandtallskog vid Tillhedstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>508059</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6783158</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2021-09-19</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>112390818</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>507998</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6783054</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>130209281</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>508033</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6783194</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>130209291</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>508080</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6783012</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>130225581</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>508257</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6783217</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>130225624</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>508161</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6783144</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>130225650</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>508027</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6783219</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinvenntering.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197008</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96221111</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112390775</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683161</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683162</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683163</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196928</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196932</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196935</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196992</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196994</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225633</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2388,6 +2468,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225634</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2490,6 +2575,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225636</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2592,6 +2682,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683147</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2694,6 +2789,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683148</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2796,6 +2896,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209297</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2903,6 +3008,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3010,6 +3120,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196934</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3117,6 +3232,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197028</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3219,6 +3339,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209299</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3325,6 +3450,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225652</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3432,6 +3562,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196984</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3539,6 +3674,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196987</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3646,6 +3786,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196988</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3753,6 +3898,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196989</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3860,6 +4010,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196990</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3967,6 +4122,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196991</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4074,6 +4234,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196996</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4181,6 +4346,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196998</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4288,6 +4458,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197001</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4395,6 +4570,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197002</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4502,6 +4682,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197003</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4616,6 +4801,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112390723</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4718,6 +4908,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209280</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4815,6 +5010,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225549</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4922,6 +5122,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197034</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5019,6 +5224,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225548</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5121,6 +5331,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225628</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5255,6 +5470,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96221156</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5362,6 +5582,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196933</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5469,6 +5694,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196936</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5576,6 +5806,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196938</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5683,6 +5918,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196939</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5790,6 +6030,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196982</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5897,6 +6142,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196983</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6004,6 +6254,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196985</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6111,6 +6366,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196997</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6218,6 +6478,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196999</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6325,6 +6590,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197000</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6432,6 +6702,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197004</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6539,6 +6814,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197005</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6636,6 +6916,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225558</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6733,6 +7018,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225559</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6830,6 +7120,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225560</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6927,6 +7222,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225561</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7024,6 +7324,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225562</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7126,6 +7431,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683146</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7228,6 +7538,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683155</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7330,6 +7645,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683157</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7432,6 +7752,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130683160</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7529,6 +7854,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225546</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7631,6 +7961,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225626</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7733,6 +8068,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209276</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7835,6 +8175,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209277</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7932,6 +8277,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225552</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8034,6 +8384,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225610</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8135,6 +8490,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209285</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8236,6 +8596,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209286</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8343,6 +8708,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196937</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8450,6 +8820,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196940</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8557,6 +8932,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197006</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8664,6 +9044,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197007</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8771,6 +9156,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197009</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8878,6 +9268,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197010</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8985,6 +9380,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96197025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9114,6 +9514,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96220942</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9248,6 +9653,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96221099</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9377,6 +9787,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96221109</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9506,6 +9921,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96221143</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9612,6 +10032,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112390786</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9714,6 +10139,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209278</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9816,6 +10246,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209293</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9918,6 +10353,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209295</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10020,6 +10460,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209301</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10122,6 +10567,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225630</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10229,6 +10679,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196929</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10336,6 +10791,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196930</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10443,6 +10903,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196995</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10544,6 +11009,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112390818</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10646,6 +11116,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209281</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10748,6 +11223,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130209291</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10854,6 +11334,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225581</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10956,6 +11441,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225624</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11062,8 +11552,113 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225650</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91441</v>
+        <v>91578</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91431</v>
+        <v>91568</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11046,6 +11046,9 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Tillhedstjärn, Dlr</t>
@@ -11101,6 +11104,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11231,10 +11235,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130225624</v>
+        <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91431</v>
+        <v>91568</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11260,16 +11264,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>508161</v>
+        <v>508257</v>
       </c>
       <c r="R97" t="n">
-        <v>6783144</v>
+        <v>6783217</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11296,12 +11303,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -11315,6 +11322,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11332,13 +11340,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130225624</t>
+          <t>https://artportalen.se/Sighting/130225581</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130225650</v>
+        <v>130225624</v>
       </c>
       <c r="B98" t="n">
         <v>91431</v>
@@ -11367,19 +11375,16 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Tillhedstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>508027</v>
+        <v>508161</v>
       </c>
       <c r="R98" t="n">
-        <v>6783219</v>
+        <v>6783144</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11406,17 +11411,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Sveaskogs naturvärdesinvenntering.</t>
+          <t>Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11425,7 +11430,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11442,6 +11446,117 @@
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225624</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>130225650</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Tillhedstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>508027</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6783219</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Sveaskogs naturvärdesinvenntering.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130225650</t>
         </is>
@@ -11546,6 +11661,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91578</v>
+        <v>91580</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91568</v>
+        <v>91570</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91568</v>
+        <v>91570</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91580</v>
+        <v>91582</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91570</v>
+        <v>91572</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91570</v>
+        <v>91572</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91582</v>
+        <v>91583</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91573</v>
+        <v>91574</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91573</v>
+        <v>91574</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91584</v>
+        <v>91585</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91574</v>
+        <v>91575</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91574</v>
+        <v>91575</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91585</v>
+        <v>91591</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91575</v>
+        <v>91581</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91575</v>
+        <v>91581</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91581</v>
+        <v>91582</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91581</v>
+        <v>91582</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91582</v>
+        <v>91588</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91582</v>
+        <v>91588</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91598</v>
+        <v>91605</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91588</v>
+        <v>91595</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91588</v>
+        <v>91595</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91595</v>
+        <v>91596</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91595</v>
+        <v>91596</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91606</v>
+        <v>91619</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91596</v>
+        <v>91609</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91596</v>
+        <v>91609</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 12767-2026 artfynd.xlsx
+++ b/artfynd/A 12767-2026 artfynd.xlsx
@@ -8395,7 +8395,7 @@
         <v>130209285</v>
       </c>
       <c r="B72" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>130209281</v>
       </c>
       <c r="B95" t="n">
-        <v>91609</v>
+        <v>91610</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>130225581</v>
       </c>
       <c r="B97" t="n">
-        <v>91609</v>
+        <v>91610</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
